--- a/excel/output_stats_vfvv/gemm/EfficiencyStats.xlsx
+++ b/excel/output_stats_vfvv/gemm/EfficiencyStats.xlsx
@@ -490,28 +490,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>52.2411</v>
+        <v>52.7449</v>
       </c>
       <c r="D2" t="n">
-        <v>20.0531</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>42.8568</v>
+        <v>43.2939</v>
       </c>
       <c r="F2" t="n">
         <v>356.29</v>
       </c>
       <c r="G2" t="n">
-        <v>357.28</v>
+        <v>358.56</v>
       </c>
       <c r="H2" t="n">
         <v>346.162</v>
       </c>
       <c r="I2" t="n">
-        <v>345.295</v>
+        <v>345.32</v>
       </c>
       <c r="J2" t="n">
-        <v>7428300000</v>
+        <v>7450060000</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
